--- a/bundles/core_workbooks/AIHE_Core_Resource_Workbooks_V1.0.xlsx
+++ b/bundles/core_workbooks/AIHE_Core_Resource_Workbooks_V1.0.xlsx
@@ -2,27 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R1e5cc606705a4019"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Index" sheetId="2" r:id="R4b83f393e52e430d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A01" sheetId="3" r:id="Rdc2d6d72533e410b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A02" sheetId="4" r:id="R2851e13cdb324f6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A03" sheetId="5" r:id="R97fb04a7428f4dc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A04" sheetId="6" r:id="R1ae05b9957114b20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C04" sheetId="7" r:id="Rcfc2f8e990ad41a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B03" sheetId="8" r:id="Ra2e49d9ccb0f4fa1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C01" sheetId="9" r:id="R9d6e85574c4e4f8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C02" sheetId="10" r:id="Rdbf7ee9d149d4aed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B01" sheetId="11" r:id="R0088dfaac9fa4021"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B02" sheetId="12" r:id="R5028fc3cc0494a7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B04" sheetId="13" r:id="R147c24e357254135"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B05" sheetId="14" r:id="R0833d9fa463f4424"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D01" sheetId="15" r:id="R7450888b2f9b4ab6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C03" sheetId="16" r:id="Rdebea7eeaf2c426e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C05" sheetId="17" r:id="R1044ae20299541a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D02" sheetId="18" r:id="R6149050c6f704cb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D03" sheetId="19" r:id="R479e91f618554c1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D04" sheetId="20" r:id="R330a147481904944"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D05" sheetId="21" r:id="R9455921e2aef4dd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R3b45cd0cf3b24e08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Index" sheetId="2" r:id="R7b591e23f4e74ec6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A01" sheetId="3" r:id="Red223197724c46a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A02" sheetId="4" r:id="R28b41ce05754403f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A03" sheetId="5" r:id="R11befa54b34d4657"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A04" sheetId="6" r:id="R0e74e1ebc1444db2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C04" sheetId="7" r:id="Rd6ef0a87491b4ee8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B03" sheetId="8" r:id="Rb38640fa11aa4136"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C01" sheetId="9" r:id="Raeca43acc53440a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C02" sheetId="10" r:id="R136e265afb884dcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B01" sheetId="11" r:id="R08bd108dcfae4a1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B02" sheetId="12" r:id="R599779851dc64a85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B04" sheetId="13" r:id="R186cf357bbc9429d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B05" sheetId="14" r:id="R5f4fa18c65b64366"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D01" sheetId="15" r:id="R9c1b7d06f2dc4696"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C03" sheetId="16" r:id="Rc8f9162e5f0e435d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C05" sheetId="17" r:id="R1d93df9a43c34f83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D02" sheetId="18" r:id="R65969a8ebcba4673"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D03" sheetId="19" r:id="R628016e447fb4167"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D04" sheetId="20" r:id="R3e286b081f264e87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D05" sheetId="21" r:id="R8ad6bf12f74d4e90"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -33,7 +33,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -55,8 +55,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF672330"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -78,6 +84,11 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F0E8"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -86,7 +97,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -146,6 +157,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -368,6 +388,13 @@
       <x:c r="B2" s="10"/>
       <x:c r="C2" s="10"/>
     </x:row>
+    <x:row r="3" ht="26" customHeight="1">
+      <x:c r="A3" s="32" t="str">
+        <x:v>Developed and maintained by the authors</x:v>
+      </x:c>
+      <x:c r="B3" s="32"/>
+      <x:c r="C3" s="32"/>
+    </x:row>
     <x:row r="4" ht="45" customHeight="1">
       <x:c r="A4" s="21" t="str">
         <x:v>Item</x:v>
@@ -476,6 +503,7 @@
   <x:mergeCells>
     <x:mergeCell ref="A1:C1"/>
     <x:mergeCell ref="A2:C2"/>
+    <x:mergeCell ref="A3:C3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/bundles/core_workbooks/AIHE_Core_Resource_Workbooks_V1.0.xlsx
+++ b/bundles/core_workbooks/AIHE_Core_Resource_Workbooks_V1.0.xlsx
@@ -2,27 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R3b45cd0cf3b24e08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Index" sheetId="2" r:id="R7b591e23f4e74ec6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A01" sheetId="3" r:id="Red223197724c46a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A02" sheetId="4" r:id="R28b41ce05754403f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A03" sheetId="5" r:id="R11befa54b34d4657"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A04" sheetId="6" r:id="R0e74e1ebc1444db2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C04" sheetId="7" r:id="Rd6ef0a87491b4ee8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B03" sheetId="8" r:id="Rb38640fa11aa4136"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C01" sheetId="9" r:id="Raeca43acc53440a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C02" sheetId="10" r:id="R136e265afb884dcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B01" sheetId="11" r:id="R08bd108dcfae4a1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B02" sheetId="12" r:id="R599779851dc64a85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B04" sheetId="13" r:id="R186cf357bbc9429d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B05" sheetId="14" r:id="R5f4fa18c65b64366"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D01" sheetId="15" r:id="R9c1b7d06f2dc4696"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C03" sheetId="16" r:id="Rc8f9162e5f0e435d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C05" sheetId="17" r:id="R1d93df9a43c34f83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D02" sheetId="18" r:id="R65969a8ebcba4673"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D03" sheetId="19" r:id="R628016e447fb4167"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D04" sheetId="20" r:id="R3e286b081f264e87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D05" sheetId="21" r:id="R8ad6bf12f74d4e90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R899dead93e6546de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Index" sheetId="2" r:id="Ra557d06abf094d4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A01" sheetId="3" r:id="R06486d223ead4e9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A02" sheetId="4" r:id="Ree0602aaf9ed436d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A03" sheetId="5" r:id="Rcd8faaabd11248bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A04" sheetId="6" r:id="Re04ee81b2968400a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C04" sheetId="7" r:id="Rb758b26329c64ad1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B03" sheetId="8" r:id="Refbb015665ab49a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C01" sheetId="9" r:id="Rcde02ba06fff48e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C02" sheetId="10" r:id="R25179326d136489e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B01" sheetId="11" r:id="Rc58f615fa5a44b32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B02" sheetId="12" r:id="R68d946692f5947bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B04" sheetId="13" r:id="R09c68a3eee884c26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B05" sheetId="14" r:id="Rb7cc3867df554745"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D01" sheetId="15" r:id="R00961e6ef0e24037"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C03" sheetId="16" r:id="R3eb628ea4f414a54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C05" sheetId="17" r:id="Raee84836a0544f34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D02" sheetId="18" r:id="R5470f67c04ea475b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D03" sheetId="19" r:id="R9758715756554235"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D04" sheetId="20" r:id="Rb9e7b6a896df481f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D05" sheetId="21" r:id="R570b32a3025c44bc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -33,7 +33,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -61,8 +61,19 @@
       <x:color rgb="FF672330"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF303033"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF6B2436"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -89,6 +100,16 @@
         <x:fgColor rgb="FFF3F0E8"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6B2436"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F0E7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -97,7 +118,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="38">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -165,6 +186,21 @@
       <x:alignment horizontal="left"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -374,25 +410,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="48" customHeight="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="33" t="str">
         <x:v>Digital Resource Companion — Core Resource Workbooks</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
+      <x:c r="B1" s="33"/>
       <x:c r="C1" s="4"/>
     </x:row>
     <x:row r="2" ht="48" customHeight="1">
-      <x:c r="A2" s="10" t="str">
+      <x:c r="A2" s="35" t="str">
         <x:v>Artificial Intelligence in Healthcare Management and Economics
 Evidence, Value, Governance, and Lifecycle Decision-Making</x:v>
       </x:c>
-      <x:c r="B2" s="10"/>
+      <x:c r="B2" s="35"/>
       <x:c r="C2" s="10"/>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="32" t="str">
+      <x:c r="A3" s="37" t="str">
         <x:v>Developed and maintained by the authors</x:v>
       </x:c>
-      <x:c r="B3" s="32"/>
+      <x:c r="B3" s="37"/>
       <x:c r="C3" s="32"/>
     </x:row>
     <x:row r="4" ht="45" customHeight="1">
@@ -416,7 +452,7 @@
         <x:v>Resource edition</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>V1.0 · 16 September 2026</x:v>
+        <x:v>V1.0 | September 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="45" customHeight="1">
@@ -488,7 +524,7 @@
         <x:v>Persistent record</x:v>
       </x:c>
       <x:c r="B15" s="24" t="str">
-        <x:v>https://doi.org/10.5281/zenodo.21753927 — Concept DOI; not a version-specific DOI for these revised files.</x:v>
+        <x:v>https://doi.org/10.5281/zenodo.21753927 — Concept DOI; cite the version-specific DOI of the archived release used.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="45" customHeight="1">
@@ -501,9 +537,9 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:C1"/>
-    <x:mergeCell ref="A2:C2"/>
-    <x:mergeCell ref="A3:C3"/>
+    <x:mergeCell ref="A1:B1"/>
+    <x:mergeCell ref="A2:B2"/>
+    <x:mergeCell ref="A3:B3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
